--- a/artfynd/A 34792-2022 artfynd.xlsx
+++ b/artfynd/A 34792-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34792-2022 artfynd.xlsx
+++ b/artfynd/A 34792-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113161712</v>
+        <v>113161709</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östiberg 4, Nb</t>
+          <t>Östiberg 7, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787846</v>
+        <v>787815</v>
       </c>
       <c r="R2" t="n">
-        <v>7355094</v>
+        <v>7355056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,14 +776,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>gammal,senvuxen</t>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # gammal,senvuxen</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113161710</v>
+        <v>113161712</v>
       </c>
       <c r="B3" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,37 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östiberg 6, Nb</t>
+          <t>Östiberg 4, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787844</v>
+        <v>787846</v>
       </c>
       <c r="R3" t="n">
-        <v>7355039</v>
+        <v>7355094</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,14 +898,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>gammal,senvuxen</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies # gammal,senvuxen</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,12 +926,7 @@
         <v>113161706</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,50 +1040,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113161711</v>
+        <v>113161707</v>
       </c>
       <c r="B5" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östiberg 5, Nb</t>
+          <t>Östiberg 9, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787894</v>
+        <v>787857</v>
       </c>
       <c r="R5" t="n">
-        <v>7355084</v>
+        <v>7355052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,50 +1142,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113161707</v>
+        <v>113161711</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östiberg 9, Nb</t>
+          <t>Östiberg 5, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787857</v>
+        <v>787894</v>
       </c>
       <c r="R6" t="n">
-        <v>7355052</v>
+        <v>7355084</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34792-2022 artfynd.xlsx
+++ b/artfynd/A 34792-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161712</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161707</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,8 +1266,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113161711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>